--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:13</t>
+    <t xml:space="preserve">2026-09-09 21:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:18</t>
+    <t xml:space="preserve">2026-09-18 09:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:13</t>
+    <t xml:space="preserve">2026-09-25 21:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -477,7 +477,7 @@
         <v>575008.69</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>189874.63</v>
+        <v>189874.62</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:34</t>
+    <t xml:space="preserve">2026-10-05 02:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -477,7 +477,7 @@
         <v>575008.69</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>189874.62</v>
+        <v>189874.63</v>
       </c>
     </row>
   </sheetData>
@@ -596,7 +596,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>802359.12</v>
+        <v>802359.13</v>
       </c>
     </row>
     <row r="5">
